--- a/ejemplos/4_Documentos_y_Actas/01_Cotizacion_EJEMPLO.xlsx
+++ b/ejemplos/4_Documentos_y_Actas/01_Cotizacion_EJEMPLO.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTADA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMATO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,80 +32,133 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="001B6B73"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="30"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <i val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="26"/>
+      <color rgb="001B6B73"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00C9D3DB"/>
+      <name val="Abadi"/>
+      <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001B6B73"/>
+      <name val="Abadi"/>
+      <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C9A227"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="002B2B2B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="005B6B78"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="008A97A3"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -135,7 +189,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -207,14 +261,28 @@
       <bottom style="thin"/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
       <top style="thick">
         <color rgb="00C9A227"/>
       </top>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="00C9A227"/>
-      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
     </border>
     <border>
       <left/>
@@ -400,101 +468,139 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="23" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="23" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -504,7 +610,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -871,22 +980,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -895,154 +1010,442 @@
       </c>
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>VERSIÓN 2.0  ·  MÉXICO</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
       <c r="D3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Cotización</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>COTIZACIÓN</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Formato administrativo editable · México</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-    </row>
-    <row r="6">
+      <c r="G5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Formato administrativo profesional · editable · listo para imprimir</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="n"/>
       <c r="D7" s="1" t="n"/>
-    </row>
-    <row r="8" ht="6" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>FÓRMULAS AUTOMÁTICAS</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>LISTAS DESPLEGABLES</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>HOJAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>LISTO PARA IMPRIMIR</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="6" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>¿QUÉ INCLUYE ESTE ARCHIVO?</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>FORMATO</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Hoja principal de captura. Aquí registras tu información; las celdas grises calculan solas.</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>AYUDA</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Preguntas frecuentes, glosario y lista de verificación para cerrar tu periodo.</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>CÓMO USARLO</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="7" t="n">
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Escribe los datos de tu empresa y del cliente.</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="B12" s="7" t="n">
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Captura las partidas con cantidad y precio unitario SIN IVA.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="7" t="n">
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Subtotal, IVA y total se calculan automáticamente.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="7" t="n">
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Edita las condiciones comerciales y envía el archivo en PDF.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="B15" s="7" t="n">
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>LEYENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Celda de captura: escribe aquí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="11" t="inlineStr"/>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Cálculo automático: no la modifiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="12" t="inlineStr"/>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Encabezados y títulos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
-        </is>
-      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Incluye alcance, exclusiones, vigencia y forma de pago para evitar malentendidos.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Numera tus cotizaciones con consecutivo y fecha.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Envía en PDF y da seguimiento a los 3 y 7 días.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Si el cliente acepta, solicita su firma o una orden de compra.</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="17" t="inlineStr"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="19" t="inlineStr"/>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="1" t="n"/>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="15">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="C28:F28"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -1068,545 +1471,613 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>COTIZACIÓN</t>
         </is>
       </c>
-      <c r="F1" s="35" t="inlineStr">
+      <c r="F1" s="50" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="G1" s="36" t="n"/>
+      <c r="G1" s="51" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="37" t="inlineStr"/>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="39" t="n"/>
+      <c r="A2" s="52" t="inlineStr"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="55" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Tu Empresa S.A. de C.V.</t>
-        </is>
-      </c>
-      <c r="C3" s="40" t="n"/>
-      <c r="D3" s="41" t="n"/>
-      <c r="E3" s="22" t="inlineStr">
-        <is>
-          <t>Folio</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>EMPRESA</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>TU EMPRESA S.A. DE C.V.</t>
+        </is>
+      </c>
+      <c r="C3" s="56" t="n"/>
+      <c r="D3" s="57" t="n"/>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>FOLIO</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>COT-2026-0142</t>
         </is>
       </c>
-      <c r="G3" s="41" t="n"/>
+      <c r="G3" s="57" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>RFC</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>TEM260101AB1</t>
         </is>
       </c>
-      <c r="C4" s="40" t="n"/>
-      <c r="D4" s="41" t="n"/>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="F4" s="23" t="n">
+      <c r="C4" s="56" t="n"/>
+      <c r="D4" s="57" t="n"/>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="n">
         <v>46302</v>
       </c>
-      <c r="G4" s="41" t="n"/>
+      <c r="G4" s="57" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Constructora Altamira S.A.</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="n"/>
-      <c r="D5" s="41" t="n"/>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>Vigencia (días)</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>CLIENTE</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>CONSTRUCTORA ALTAMIRA S.A.</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="n"/>
+      <c r="D5" s="57" t="n"/>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>VIGENCIA (DÍAS)</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="41" t="n"/>
+      <c r="G5" s="57" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>Contacto</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Ing. Roberto Salas</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="n"/>
-      <c r="D6" s="41" t="n"/>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>Tel. / Correo</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>CONTACTO</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>ING. ROBERTO SALAS</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="n"/>
+      <c r="D6" s="57" t="n"/>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>TEL. / CORREO</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>55 1234 5678</t>
         </is>
       </c>
-      <c r="G6" s="41" t="n"/>
+      <c r="G6" s="57" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>Part.</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Clave</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>Precio unit.</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>Importe</t>
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>PART.</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>CLAVE</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>UNIDAD</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>CANTIDAD</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT.</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>IMPORTE</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>SRV-01</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Diagnóstico administrativo</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="E9" s="26" t="n">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>DIAGNÓSTICO ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>SERVICIO</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="34" t="n">
         <v>18500</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="35">
         <f>IF(E9="","",E9*F9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>SRV-02</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Implementación de control de inventarios</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="E10" s="26" t="n">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>IMPLEMENTACIÓN DE CONTROL DE INVENTARIOS</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>SERVICIO</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="34" t="n">
         <v>32000</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="35">
         <f>IF(E10="","",E10*F10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>CAP-01</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Capacitación al personal (8 horas)</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Curso</t>
-        </is>
-      </c>
-      <c r="E11" s="26" t="n">
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>CAPACITACIÓN AL PERSONAL (8 HORAS)</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>CURSO</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="34" t="n">
         <v>6500</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="35">
         <f>IF(E11="","",E11*F11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>SOP-01</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Soporte mensual (3 meses)</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="E12" s="26" t="n">
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>SOPORTE MENSUAL (3 MESES)</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>MES</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="34" t="n">
         <v>4200</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="35">
         <f>IF(E12="","",E12*F12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="n">
+      <c r="A13" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="28">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="33" t="n"/>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="35">
         <f>IF(E13="","",E13*F13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="28">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="33" t="n"/>
+      <c r="F14" s="34" t="n"/>
+      <c r="G14" s="35">
         <f>IF(E14="","",E14*F14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="28">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="33" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="35">
         <f>IF(E15="","",E15*F15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="28">
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="33" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="35">
         <f>IF(E16="","",E16*F16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="28">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="33" t="n"/>
+      <c r="F17" s="34" t="n"/>
+      <c r="G17" s="35">
         <f>IF(E17="","",E17*F17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="28">
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="33" t="n"/>
+      <c r="F18" s="34" t="n"/>
+      <c r="G18" s="35">
         <f>IF(E18="","",E18*F18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="28">
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="33" t="n"/>
+      <c r="F19" s="34" t="n"/>
+      <c r="G19" s="35">
         <f>IF(E19="","",E19*F19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="28">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="34" t="n"/>
+      <c r="G20" s="35">
         <f>IF(E20="","",E20*F20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="n">
+      <c r="A21" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="28">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="33" t="n"/>
+      <c r="F21" s="34" t="n"/>
+      <c r="G21" s="35">
         <f>IF(E21="","",E21*F21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="28">
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="35">
         <f>IF(E22="","",E22*F22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="n">
+      <c r="A23" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="28">
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="33" t="n"/>
+      <c r="F23" s="34" t="n"/>
+      <c r="G23" s="35">
         <f>IF(E23="","",E23*F23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="F24" s="29" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="G24" s="30">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="36" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="G24" s="37">
         <f>SUM(G9:G23)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="F25" s="29" t="inlineStr">
-        <is>
-          <t>Descuento</t>
-        </is>
-      </c>
-      <c r="G25" s="27" t="n">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="36" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G25" s="34" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="26">
-      <c r="F26" s="29" t="inlineStr">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="36" t="inlineStr">
         <is>
           <t>IVA 16%</t>
         </is>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="37">
         <f>ROUND((G24-G25)*0.16,2)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="F27" s="29" t="inlineStr">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="36" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="37">
         <f>G24-G25+G26</f>
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="31" t="inlineStr">
-        <is>
-          <t>Condiciones comerciales:</t>
-        </is>
-      </c>
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>CONDICIONES COMERCIALES:</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Precios en pesos mexicanos (MXN) más IVA, salvo indicación.
-• Forma de pago: 
-• Tiempo de entrega: 
-• Vigencia de la cotización: </t>
-        </is>
-      </c>
-      <c r="B30" s="42" t="n"/>
-      <c r="C30" s="42" t="n"/>
-      <c r="D30" s="42" t="n"/>
-      <c r="E30" s="42" t="n"/>
-      <c r="F30" s="42" t="n"/>
-      <c r="G30" s="43" t="n"/>
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• PRECIOS EN PESOS MEXICANOS (MXN) MÁS IVA, SALVO INDICACIÓN.
+• FORMA DE PAGO: 
+• TIEMPO DE ENTREGA: 
+• VIGENCIA DE LA COTIZACIÓN: </t>
+        </is>
+      </c>
+      <c r="B30" s="58" t="n"/>
+      <c r="C30" s="58" t="n"/>
+      <c r="D30" s="58" t="n"/>
+      <c r="E30" s="58" t="n"/>
+      <c r="F30" s="58" t="n"/>
+      <c r="G30" s="59" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="44" t="n"/>
-      <c r="B31" s="45" t="n"/>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="45" t="n"/>
-      <c r="F31" s="45" t="n"/>
-      <c r="G31" s="46" t="n"/>
+      <c r="A31" s="60" t="n"/>
+      <c r="B31" s="61" t="n"/>
+      <c r="C31" s="61" t="n"/>
+      <c r="D31" s="61" t="n"/>
+      <c r="E31" s="61" t="n"/>
+      <c r="F31" s="61" t="n"/>
+      <c r="G31" s="62" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="44" t="n"/>
-      <c r="B32" s="45" t="n"/>
-      <c r="C32" s="45" t="n"/>
-      <c r="D32" s="45" t="n"/>
-      <c r="E32" s="45" t="n"/>
-      <c r="F32" s="45" t="n"/>
-      <c r="G32" s="46" t="n"/>
+      <c r="A32" s="60" t="n"/>
+      <c r="B32" s="61" t="n"/>
+      <c r="C32" s="61" t="n"/>
+      <c r="D32" s="61" t="n"/>
+      <c r="E32" s="61" t="n"/>
+      <c r="F32" s="61" t="n"/>
+      <c r="G32" s="62" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="47" t="n"/>
-      <c r="B33" s="48" t="n"/>
-      <c r="C33" s="48" t="n"/>
-      <c r="D33" s="48" t="n"/>
-      <c r="E33" s="48" t="n"/>
-      <c r="F33" s="48" t="n"/>
-      <c r="G33" s="49" t="n"/>
+      <c r="A33" s="63" t="n"/>
+      <c r="B33" s="64" t="n"/>
+      <c r="C33" s="64" t="n"/>
+      <c r="D33" s="64" t="n"/>
+      <c r="E33" s="64" t="n"/>
+      <c r="F33" s="64" t="n"/>
+      <c r="G33" s="65" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="33" t="n"/>
-      <c r="B36" s="50" t="n"/>
-      <c r="D36" s="33" t="n"/>
-      <c r="E36" s="50" t="n"/>
+      <c r="A36" s="40" t="n"/>
+      <c r="B36" s="66" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="66" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="34" t="inlineStr">
-        <is>
-          <t>Atentamente</t>
-        </is>
-      </c>
-      <c r="D37" s="34" t="inlineStr">
-        <is>
-          <t>Aceptación del cliente</t>
-        </is>
-      </c>
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>ATENTAMENTE</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="41" t="inlineStr">
+        <is>
+          <t>ACEPTACIÓN DEL CLIENTE</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -1640,4 +2111,341 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B6B73"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="42" t="inlineStr">
+        <is>
+          <t>AYUDA Y PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>COTIZACIÓN</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>¿Cuál es la vigencia normal?</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="inlineStr">
+        <is>
+          <t>Entre 15 y 30 días, según la volatilidad de tus costos.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>¿Cómo agrego un descuento?</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="inlineStr">
+        <is>
+          <t>Escribe el importe en la celda Descuento; el IVA se calcula sobre el subtotal neto.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>¿Por qué no puedo escribir en algunas celdas?</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="inlineStr">
+        <is>
+          <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>¿Cómo agrego mi logotipo?</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="inlineStr">
+        <is>
+          <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
+        </is>
+      </c>
+      <c r="D10" s="45" t="inlineStr">
+        <is>
+          <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>¿Con qué versiones de Excel funciona?</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>¿Por qué la letra se ve diferente?</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>¿Puedo usarlo en varias empresas o por varios años?</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="inlineStr">
+        <is>
+          <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>GLOSARIO</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>Suma de partidas antes de impuestos.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="inlineStr">
+        <is>
+          <t>Impuesto al Valor Agregado, 16% en la mayor parte del país.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>VIGENCIA</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>Periodo durante el cual los precios son válidos.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>LISTA DE VERIFICACIÓN (marca ☑ al completar)</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="inlineStr">
+        <is>
+          <t>Datos del cliente correctos</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="inlineStr">
+        <is>
+          <t>Alcance y exclusiones definidos</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>Condiciones comerciales completas</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>Enviada y con fecha de seguimiento</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"☐,☑"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/ejemplos/4_Documentos_y_Actas/01_Cotizacion_EJEMPLO.xlsx
+++ b/ejemplos/4_Documentos_y_Actas/01_Cotizacion_EJEMPLO.xlsx
@@ -52,7 +52,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -96,7 +96,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -119,7 +119,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -147,7 +147,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -2116,7 +2116,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/ejemplos/4_Documentos_y_Actas/01_Cotizacion_EJEMPLO.xlsx
+++ b/ejemplos/4_Documentos_y_Actas/01_Cotizacion_EJEMPLO.xlsx
@@ -1005,7 +1005,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1421,7 +1421,7 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="G37" s="1" t="n"/>

--- a/ejemplos/4_Documentos_y_Actas/01_Cotizacion_EJEMPLO.xlsx
+++ b/ejemplos/4_Documentos_y_Actas/01_Cotizacion_EJEMPLO.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMATO" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FORMATO'!$8:$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -23,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,136 +34,143 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="30"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E7C8B"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
-      <color rgb="002B2B2B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -184,12 +193,27 @@
       </patternFill>
     </fill>
     <fill>
+      <gradientFill type="linear" degree="90">
+        <stop position="0">
+          <color rgb="0017426B"/>
+        </stop>
+        <stop position="1">
+          <color rgb="000B2A4A"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="30">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -258,6 +282,20 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
       <bottom style="thin"/>
     </border>
     <border>
@@ -281,8 +319,22 @@
     </border>
     <border>
       <bottom style="thin">
+        <color rgb="00E3E8ED"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
         <color rgb="00C9D3DB"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E3E8ED"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -468,24 +520,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -496,19 +548,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -517,103 +577,115 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="24" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="24" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="24" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -980,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1200,7 +1272,7 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>CÓMO USARLO</t>
+          <t>FICHA TÉCNICA</t>
         </is>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -1211,62 +1283,87 @@
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="4" t="n"/>
-      <c r="B20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Escribe los datos de tu empresa y del cliente.</t>
-        </is>
-      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Capacidad</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>15 partidas</t>
+        </is>
+      </c>
+      <c r="E20" s="56" t="n"/>
+      <c r="F20" s="56" t="n"/>
       <c r="G20" s="4" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Captura las partidas con cantidad y precio unitario SIN IVA.</t>
-        </is>
-      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Compatibilidad</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac)</t>
+        </is>
+      </c>
+      <c r="E21" s="56" t="n"/>
+      <c r="F21" s="56" t="n"/>
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Subtotal, IVA y total se calculan automáticamente.</t>
-        </is>
-      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Idioma y moneda</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Español (México) · Pesos mexicanos (MXN) · IVA 16%</t>
+        </is>
+      </c>
+      <c r="E22" s="56" t="n"/>
+      <c r="F22" s="56" t="n"/>
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Edita las condiciones comerciales y envía el archivo en PDF.</t>
-        </is>
-      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Protección</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Hojas protegidas sin contraseña (Revisar &gt; Desproteger hoja)</t>
+        </is>
+      </c>
+      <c r="E23" s="56" t="n"/>
+      <c r="F23" s="56" t="n"/>
       <c r="G23" s="4" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="21" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Arial (disponible en Windows, Mac y Google Sheets)</t>
+        </is>
+      </c>
+      <c r="E24" s="56" t="n"/>
+      <c r="F24" s="56" t="n"/>
       <c r="G24" s="4" t="n"/>
     </row>
     <row r="25">
@@ -1282,7 +1379,7 @@
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>RECOMENDACIONES DE USO</t>
+          <t>CÓMO USARLO</t>
         </is>
       </c>
       <c r="C26" s="10" t="n"/>
@@ -1293,158 +1390,262 @@
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="4" t="n"/>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B27" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Incluye alcance, exclusiones, vigencia y forma de pago para evitar malentendidos.</t>
+          <t>Escribe los datos de tu empresa y del cliente.</t>
         </is>
       </c>
       <c r="G27" s="4" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B28" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>Numera tus cotizaciones con consecutivo y fecha.</t>
+          <t>Captura las partidas con cantidad y precio unitario SIN IVA.</t>
         </is>
       </c>
       <c r="G28" s="4" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B29" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Envía en PDF y da seguimiento a los 3 y 7 días.</t>
+          <t>Subtotal, IVA y total se calculan automáticamente.</t>
         </is>
       </c>
       <c r="G29" s="4" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Edita las condiciones comerciales y envía el archivo en PDF.</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Incluye alcance, exclusiones, vigencia y forma de pago para evitar malentendidos.</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Numera tus cotizaciones con consecutivo y fecha.</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Envía en PDF y da seguimiento a los 3 y 7 días.</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Si el cliente acepta, solicita su firma o una orden de compra.</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>LEYENDA DE COLORES</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="17" t="inlineStr"/>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>CELDA DE CAPTURA: escribe aquí.</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="19" t="inlineStr"/>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="22" t="inlineStr"/>
+      <c r="C41" s="21" t="inlineStr">
         <is>
           <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="20" t="inlineStr"/>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="23" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>ENCABEZADOS Y TÍTULOS.</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-    </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="24" t="inlineStr"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>* CAMPO OBLIGATORIO: complétalo antes de imprimir o enviar.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="1" t="n"/>
+      <c r="B45" s="25" t="inlineStr">
         <is>
           <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
-      <c r="G37" s="1" t="n"/>
+      <c r="G45" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="15">
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
+  <mergeCells count="20">
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B4:F5"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId2"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
@@ -1461,7 +1662,7 @@
   <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.2" customWidth="1" min="1" max="1"/>
+    <col width="12.35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1471,123 +1672,123 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>COTIZACIÓN</t>
         </is>
       </c>
-      <c r="F1" s="50" t="inlineStr">
+      <c r="F1" s="57" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="G1" s="51" t="n"/>
+      <c r="G1" s="58" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="52" t="inlineStr"/>
-      <c r="B2" s="53" t="n"/>
-      <c r="C2" s="53" t="n"/>
-      <c r="D2" s="53" t="n"/>
-      <c r="E2" s="53" t="n"/>
-      <c r="F2" s="54" t="n"/>
-      <c r="G2" s="55" t="n"/>
+      <c r="A2" s="59" t="inlineStr"/>
+      <c r="B2" s="60" t="n"/>
+      <c r="C2" s="60" t="n"/>
+      <c r="D2" s="60" t="n"/>
+      <c r="E2" s="60" t="n"/>
+      <c r="F2" s="61" t="n"/>
+      <c r="G2" s="62" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
-        <is>
-          <t>EMPRESA</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
+        <is>
+          <t>EMPRESA *</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>TU EMPRESA S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="C3" s="56" t="n"/>
-      <c r="D3" s="57" t="n"/>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t>FOLIO</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="C3" s="63" t="n"/>
+      <c r="D3" s="64" t="n"/>
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>FOLIO *</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>COT-2026-0142</t>
         </is>
       </c>
-      <c r="G3" s="57" t="n"/>
+      <c r="G3" s="64" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>RFC</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>TEM260101AB1</t>
         </is>
       </c>
-      <c r="C4" s="56" t="n"/>
-      <c r="D4" s="57" t="n"/>
-      <c r="E4" s="29" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F4" s="30" t="n">
+      <c r="C4" s="63" t="n"/>
+      <c r="D4" s="64" t="n"/>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>FECHA *</t>
+        </is>
+      </c>
+      <c r="F4" s="34" t="n">
         <v>46302</v>
       </c>
-      <c r="G4" s="57" t="n"/>
+      <c r="G4" s="64" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
-        <is>
-          <t>CLIENTE</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>CLIENTE *</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>CONSTRUCTORA ALTAMIRA S.A.</t>
         </is>
       </c>
-      <c r="C5" s="56" t="n"/>
-      <c r="D5" s="57" t="n"/>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="C5" s="63" t="n"/>
+      <c r="D5" s="64" t="n"/>
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>VIGENCIA (DÍAS)</t>
         </is>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="57" t="n"/>
+      <c r="G5" s="64" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>CONTACTO</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>ING. ROBERTO SALAS</t>
         </is>
       </c>
-      <c r="C6" s="56" t="n"/>
-      <c r="D6" s="57" t="n"/>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="C6" s="63" t="n"/>
+      <c r="D6" s="64" t="n"/>
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>TEL. / CORREO</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>55 1234 5678</t>
         </is>
       </c>
-      <c r="G6" s="57" t="n"/>
+      <c r="G6" s="64" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
@@ -1598,313 +1799,313 @@
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>PART.</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>CLAVE</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>DESCRIPCIÓN</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>CANTIDAD</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>PRECIO UNIT.</t>
         </is>
       </c>
-      <c r="G8" s="31" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>IMPORTE</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="32" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>SRV-01</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>DIAGNÓSTICO ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>SERVICIO</t>
         </is>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="39" t="n">
         <v>18500</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="40">
         <f>IF(E9="","",E9*F9)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="32" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>SRV-02</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>IMPLEMENTACIÓN DE CONTROL DE INVENTARIOS</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>SERVICIO</t>
         </is>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F10" s="39" t="n">
         <v>32000</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="40">
         <f>IF(E10="","",E10*F10)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="32" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>CAP-01</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>CAPACITACIÓN AL PERSONAL (8 HORAS)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>CURSO</t>
         </is>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F11" s="39" t="n">
         <v>6500</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="40">
         <f>IF(E11="","",E11*F11)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="32" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>SOP-01</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>SOPORTE MENSUAL (3 MESES)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>MES</t>
         </is>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F12" s="39" t="n">
         <v>4200</v>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="40">
         <f>IF(E12="","",E12*F12)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="32" t="n">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="34" t="n"/>
-      <c r="G13" s="35">
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="40">
         <f>IF(E13="","",E13*F13)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="32" t="n">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="33" t="n"/>
-      <c r="F14" s="34" t="n"/>
-      <c r="G14" s="35">
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="40">
         <f>IF(E14="","",E14*F14)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="32" t="n">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="34" t="n"/>
-      <c r="G15" s="35">
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="40">
         <f>IF(E15="","",E15*F15)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="32" t="n">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="33" t="n"/>
-      <c r="F16" s="34" t="n"/>
-      <c r="G16" s="35">
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="38" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="40">
         <f>IF(E16="","",E16*F16)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="32" t="n">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="33" t="n"/>
-      <c r="F17" s="34" t="n"/>
-      <c r="G17" s="35">
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="38" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="40">
         <f>IF(E17="","",E17*F17)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="32" t="n">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="33" t="n"/>
-      <c r="F18" s="34" t="n"/>
-      <c r="G18" s="35">
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="38" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="40">
         <f>IF(E18="","",E18*F18)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="32" t="n">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="33" t="n"/>
-      <c r="F19" s="34" t="n"/>
-      <c r="G19" s="35">
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="38" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="40">
         <f>IF(E19="","",E19*F19)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="32" t="n">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="33" t="n"/>
-      <c r="F20" s="34" t="n"/>
-      <c r="G20" s="35">
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="40">
         <f>IF(E20="","",E20*F20)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="32" t="n">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="33" t="n"/>
-      <c r="F21" s="34" t="n"/>
-      <c r="G21" s="35">
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="37" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="40">
         <f>IF(E21="","",E21*F21)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="32" t="n">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="33" t="n"/>
-      <c r="F22" s="34" t="n"/>
-      <c r="G22" s="35">
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="38" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="40">
         <f>IF(E22="","",E22*F22)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="32" t="n">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="33" t="n"/>
-      <c r="F23" s="34" t="n"/>
-      <c r="G23" s="35">
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="38" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="40">
         <f>IF(E23="","",E23*F23)</f>
         <v/>
       </c>
@@ -1915,12 +2116,12 @@
       <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
-      <c r="F24" s="36" t="inlineStr">
+      <c r="F24" s="41" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="42">
         <f>SUM(G9:G23)</f>
         <v/>
       </c>
@@ -1931,12 +2132,12 @@
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
-      <c r="F25" s="36" t="inlineStr">
+      <c r="F25" s="41" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G25" s="34" t="n">
+      <c r="G25" s="43" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -1946,12 +2147,12 @@
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
-      <c r="F26" s="36" t="inlineStr">
+      <c r="F26" s="41" t="inlineStr">
         <is>
           <t>IVA 16%</t>
         </is>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="42">
         <f>ROUND((G24-G25)*0.16,2)</f>
         <v/>
       </c>
@@ -1962,12 +2163,12 @@
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
-      <c r="F27" s="36" t="inlineStr">
+      <c r="F27" s="41" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="G27" s="37">
+      <c r="G27" s="42">
         <f>G24-G25+G26</f>
         <v/>
       </c>
@@ -1982,7 +2183,7 @@
       <c r="G28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="44" t="inlineStr">
         <is>
           <t>CONDICIONES COMERCIALES:</t>
         </is>
@@ -1995,7 +2196,7 @@
       <c r="G29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve">• PRECIOS EN PESOS MEXICANOS (MXN) MÁS IVA, SALVO INDICACIÓN.
 • FORMA DE PAGO: 
@@ -2003,39 +2204,39 @@
 • VIGENCIA DE LA COTIZACIÓN: </t>
         </is>
       </c>
-      <c r="B30" s="58" t="n"/>
-      <c r="C30" s="58" t="n"/>
-      <c r="D30" s="58" t="n"/>
-      <c r="E30" s="58" t="n"/>
-      <c r="F30" s="58" t="n"/>
-      <c r="G30" s="59" t="n"/>
+      <c r="B30" s="65" t="n"/>
+      <c r="C30" s="65" t="n"/>
+      <c r="D30" s="65" t="n"/>
+      <c r="E30" s="65" t="n"/>
+      <c r="F30" s="65" t="n"/>
+      <c r="G30" s="66" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="n"/>
-      <c r="B31" s="61" t="n"/>
-      <c r="C31" s="61" t="n"/>
-      <c r="D31" s="61" t="n"/>
-      <c r="E31" s="61" t="n"/>
-      <c r="F31" s="61" t="n"/>
-      <c r="G31" s="62" t="n"/>
+      <c r="A31" s="67" t="n"/>
+      <c r="B31" s="68" t="n"/>
+      <c r="C31" s="68" t="n"/>
+      <c r="D31" s="68" t="n"/>
+      <c r="E31" s="68" t="n"/>
+      <c r="F31" s="68" t="n"/>
+      <c r="G31" s="69" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="60" t="n"/>
-      <c r="B32" s="61" t="n"/>
-      <c r="C32" s="61" t="n"/>
-      <c r="D32" s="61" t="n"/>
-      <c r="E32" s="61" t="n"/>
-      <c r="F32" s="61" t="n"/>
-      <c r="G32" s="62" t="n"/>
+      <c r="A32" s="67" t="n"/>
+      <c r="B32" s="68" t="n"/>
+      <c r="C32" s="68" t="n"/>
+      <c r="D32" s="68" t="n"/>
+      <c r="E32" s="68" t="n"/>
+      <c r="F32" s="68" t="n"/>
+      <c r="G32" s="69" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="63" t="n"/>
-      <c r="B33" s="64" t="n"/>
-      <c r="C33" s="64" t="n"/>
-      <c r="D33" s="64" t="n"/>
-      <c r="E33" s="64" t="n"/>
-      <c r="F33" s="64" t="n"/>
-      <c r="G33" s="65" t="n"/>
+      <c r="A33" s="70" t="n"/>
+      <c r="B33" s="71" t="n"/>
+      <c r="C33" s="71" t="n"/>
+      <c r="D33" s="71" t="n"/>
+      <c r="E33" s="71" t="n"/>
+      <c r="F33" s="71" t="n"/>
+      <c r="G33" s="72" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -2056,22 +2257,22 @@
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="40" t="n"/>
-      <c r="B36" s="66" t="n"/>
+      <c r="A36" s="46" t="n"/>
+      <c r="B36" s="73" t="n"/>
       <c r="C36" s="4" t="n"/>
-      <c r="D36" s="40" t="n"/>
-      <c r="E36" s="66" t="n"/>
+      <c r="D36" s="46" t="n"/>
+      <c r="E36" s="73" t="n"/>
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="47" t="inlineStr">
         <is>
           <t>ATENTAMENTE</t>
         </is>
       </c>
       <c r="C37" s="4" t="n"/>
-      <c r="D37" s="41" t="inlineStr">
+      <c r="D37" s="47" t="inlineStr">
         <is>
           <t>ACEPTACIÓN DEL CLIENTE</t>
         </is>
@@ -2099,6 +2300,11 @@
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="A30:G33"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F9:F23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
@@ -2132,7 +2338,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="42" t="inlineStr">
+      <c r="B1" s="48" t="inlineStr">
         <is>
           <t>AYUDA Y PREGUNTAS FRECUENTES</t>
         </is>
@@ -2141,7 +2347,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="43" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>COTIZACIÓN</t>
         </is>
@@ -2176,12 +2382,12 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>¿Cuál es la vigencia normal?</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="51" t="inlineStr">
         <is>
           <t>Entre 15 y 30 días, según la volatilidad de tus costos.</t>
         </is>
@@ -2191,12 +2397,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
         <is>
           <t>¿Cómo agrego un descuento?</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="51" t="inlineStr">
         <is>
           <t>Escribe el importe en la celda Descuento; el IVA se calcula sobre el subtotal neto.</t>
         </is>
@@ -2206,12 +2412,12 @@
     <row r="8" ht="53" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>¿Por qué no puedo escribir en algunas celdas?</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="51" t="inlineStr">
         <is>
           <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
         </is>
@@ -2221,12 +2427,12 @@
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
         <is>
           <t>¿Cómo agrego mi logotipo?</t>
         </is>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="51" t="inlineStr">
         <is>
           <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
         </is>
@@ -2236,12 +2442,12 @@
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
         </is>
       </c>
-      <c r="D10" s="45" t="inlineStr">
+      <c r="D10" s="51" t="inlineStr">
         <is>
           <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
         </is>
@@ -2251,12 +2457,12 @@
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="44" t="inlineStr">
+      <c r="C11" s="50" t="inlineStr">
         <is>
           <t>¿Con qué versiones de Excel funciona?</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="51" t="inlineStr">
         <is>
           <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
         </is>
@@ -2266,14 +2472,14 @@
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
-      <c r="C12" s="44" t="inlineStr">
-        <is>
-          <t>¿Por qué la letra se ve diferente?</t>
-        </is>
-      </c>
-      <c r="D12" s="45" t="inlineStr">
-        <is>
-          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>¿Puedo cambiar la letra?</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Arial, disponible en Windows, Mac y Google Sheets. Si necesitas otra, selecciona todo (Ctrl+E) y cambia la fuente; no afecta el funcionamiento.</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -2281,12 +2487,12 @@
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>¿Puedo usarlo en varias empresas o por varios años?</t>
         </is>
       </c>
-      <c r="D13" s="45" t="inlineStr">
+      <c r="D13" s="51" t="inlineStr">
         <is>
           <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
         </is>
@@ -2314,12 +2520,12 @@
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="52" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="D16" s="47" t="inlineStr">
+      <c r="D16" s="53" t="inlineStr">
         <is>
           <t>Suma de partidas antes de impuestos.</t>
         </is>
@@ -2329,12 +2535,12 @@
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="52" t="inlineStr">
         <is>
           <t>IVA</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="53" t="inlineStr">
         <is>
           <t>Impuesto al Valor Agregado, 16% en la mayor parte del país.</t>
         </is>
@@ -2344,12 +2550,12 @@
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="52" t="inlineStr">
         <is>
           <t>VIGENCIA</t>
         </is>
       </c>
-      <c r="D18" s="47" t="inlineStr">
+      <c r="D18" s="53" t="inlineStr">
         <is>
           <t>Periodo durante el cual los precios son válidos.</t>
         </is>
@@ -2376,12 +2582,12 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="48" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C21" s="49" t="inlineStr">
+      <c r="C21" s="55" t="inlineStr">
         <is>
           <t>Datos del cliente correctos</t>
         </is>
@@ -2390,12 +2596,12 @@
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="48" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C22" s="49" t="inlineStr">
+      <c r="C22" s="55" t="inlineStr">
         <is>
           <t>Alcance y exclusiones definidos</t>
         </is>
@@ -2404,12 +2610,12 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="48" t="inlineStr">
+      <c r="B23" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C23" s="49" t="inlineStr">
+      <c r="C23" s="55" t="inlineStr">
         <is>
           <t>Condiciones comerciales completas</t>
         </is>
@@ -2418,12 +2624,12 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="48" t="inlineStr">
+      <c r="B24" s="54" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C24" s="49" t="inlineStr">
+      <c r="C24" s="55" t="inlineStr">
         <is>
           <t>Enviada y con fecha de seguimiento</t>
         </is>
